--- a/survey_templates/039_customer_feedback_audit_form--survey_templates.xlsx
+++ b/survey_templates/039_customer_feedback_audit_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>customer_feedback</t>
+          <t>customer_feedback_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>customer_experience</t>
+          <t>customer_experience_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>customer_satisfaction</t>
+          <t>customer_satisfaction_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Customer Satisfaction 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>service_quality</t>
+          <t>service_quality_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>Service Quality 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>product_quality</t>
+          <t>product_quality_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Product Quality</t>
+          <t>Product Quality 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>customer_service</t>
+          <t>customer_service_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Customer Service 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>product_quality</t>
+          <t>product_quality_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Product Quality</t>
+          <t>Product Quality 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_"don't_know"}</t>
+          <t>don't_know</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': "Don't know"}</t>
+          <t>Don't know</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_prophets'}</t>
+          <t>very_prophets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very prophets'}</t>
+          <t>Very prophets</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1301,114 +1301,114 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>service_quality_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>service_quality_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>service_quality_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>product_quality_choices</t>
+          <t>product_quality_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>product_quality_choices</t>
+          <t>product_quality_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>product_quality_choices</t>
+          <t>product_quality_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
@@ -1454,97 +1454,97 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>customer_service_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>customer_service_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>customer_service_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>product_quality_choices</t>
+          <t>product_quality_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>product_quality_choices</t>
+          <t>product_quality_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_good'}</t>
+          <t>not_very_good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Not very good'}</t>
+          <t>Not very good</t>
         </is>
       </c>
     </row>
